--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MISSOURI_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/MISSOURI_2014.xlsx
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C71">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C111">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C188">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C195">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C429">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C467">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C475">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C702">
